--- a/data/modeles_recepta/P4_Rural_1x2_1km.xlsx
+++ b/data/modeles_recepta/P4_Rural_1x2_1km.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEGENDE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LEGENDE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PK_Coordonnees" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="OFFSETS_TRANSVERSAUX" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PK_Coordonnees'!$A$3:$F$45</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="+0.000;-0.000;0.000"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +72,77 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="000F4C35"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00475569"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F766E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -135,8 +214,58 @@
         <fgColor rgb="000D1F38"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F4C35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,11 +287,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -239,6 +382,87 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -313,36 +537,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9334500" cy="3429000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4722,6 +4916,1351 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>COORDONNÉES DE L'AXE — Route Rurale 1x2 voies — 1 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Système de référence : Lambert 93 (EPSG:2154)  —  Données à renseigner avec les coordonnées réelles du levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>X (m)</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Y (m)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Z axe (m)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Gisement (°)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>Dist. cumulée (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Point kilométrique</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Lambert 93 — Est</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Lambert 93 — Nord</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>Cote NGF de l'axe chaussée</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Direction route (0°=N, 90°=E)</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>Distance depuis l'origine</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>0+000</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n">
+        <v>833650</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>6520100</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>142.78</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>285</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>0+025</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n">
+        <v>833625.862</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>6520106.51</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>142.692</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>285.0937</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>0+050</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n">
+        <v>833601.746</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>6520113.099</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>142.605</v>
+      </c>
+      <c r="E7" s="38" t="n">
+        <v>285.1874</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>0+075</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>833577.652</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>6520119.766</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>142.518</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>285.2808</v>
+      </c>
+      <c r="F8" s="39" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>0+100</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="n">
+        <v>833553.578</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>6520126.512</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>142.43</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>285.374</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>0+125</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>833529.527</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>6520133.335</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>142.343</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>285.4668</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>0+150</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>833505.497</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>6520140.235</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>142.255</v>
+      </c>
+      <c r="E11" s="38" t="n">
+        <v>285.5592</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>0+175</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>833481.4889999999</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>6520147.211</v>
+      </c>
+      <c r="D12" s="37" t="n">
+        <v>142.167</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>285.651</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>0+200</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n">
+        <v>833457.502</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>6520154.262</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>142.08</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>285.7422</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>0+225</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="n">
+        <v>833433.536</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>6520161.386</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>141.993</v>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>285.8327</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>0+250</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="n">
+        <v>833409.591</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>6520168.583</v>
+      </c>
+      <c r="D15" s="37" t="n">
+        <v>141.905</v>
+      </c>
+      <c r="E15" s="38" t="n">
+        <v>285.9223</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>0+275</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n">
+        <v>833385.6679999999</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>6520175.851</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>141.817</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>286.0111</v>
+      </c>
+      <c r="F16" s="39" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>0+300</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>833361.765</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>6520183.188</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>141.73</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>286.0988</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>0+325</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="n">
+        <v>833337.882</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>6520190.593</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>141.643</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>286.1855</v>
+      </c>
+      <c r="F18" s="39" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>0+350</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="n">
+        <v>833314.019</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>6520198.063</v>
+      </c>
+      <c r="D19" s="37" t="n">
+        <v>141.555</v>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>286.271</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>0+375</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="n">
+        <v>833290.175</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>6520205.597</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <v>141.468</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>286.3553</v>
+      </c>
+      <c r="F20" s="39" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>0+400</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>833266.35</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>6520213.193</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>141.38</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>286.4383</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>0+425</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n">
+        <v>833242.5429999999</v>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>6520220.848</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <v>141.292</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>286.5198</v>
+      </c>
+      <c r="F22" s="39" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>0+450</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="n">
+        <v>833218.755</v>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>6520228.559</v>
+      </c>
+      <c r="D23" s="37" t="n">
+        <v>141.205</v>
+      </c>
+      <c r="E23" s="38" t="n">
+        <v>286.5999</v>
+      </c>
+      <c r="F23" s="39" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>0+475</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n">
+        <v>833194.983</v>
+      </c>
+      <c r="C24" s="36" t="n">
+        <v>6520236.325</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>141.118</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>286.6784</v>
+      </c>
+      <c r="F24" s="39" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>0+500</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n">
+        <v>833171.228</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <v>6520244.142</v>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>141.03</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>286.7553</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>0+525</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n">
+        <v>833147.488</v>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>6520252.009</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>140.942</v>
+      </c>
+      <c r="E26" s="38" t="n">
+        <v>286.8305</v>
+      </c>
+      <c r="F26" s="39" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>0+550</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n">
+        <v>833123.763</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>6520259.921</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>140.855</v>
+      </c>
+      <c r="E27" s="38" t="n">
+        <v>286.9038</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>0+575</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n">
+        <v>833100.052</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>6520267.877</v>
+      </c>
+      <c r="D28" s="37" t="n">
+        <v>140.768</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>286.9753</v>
+      </c>
+      <c r="F28" s="39" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>0+600</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n">
+        <v>833076.355</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>6520275.873</v>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>140.68</v>
+      </c>
+      <c r="E29" s="33" t="n">
+        <v>287.0449</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>0+625</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n">
+        <v>833052.669</v>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>6520283.906</v>
+      </c>
+      <c r="D30" s="37" t="n">
+        <v>140.593</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>287.1125</v>
+      </c>
+      <c r="F30" s="39" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>0+650</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>833028.995</v>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>6520291.972</v>
+      </c>
+      <c r="D31" s="37" t="n">
+        <v>140.505</v>
+      </c>
+      <c r="E31" s="38" t="n">
+        <v>287.178</v>
+      </c>
+      <c r="F31" s="39" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>0+675</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>833005.3320000001</v>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>6520300.069</v>
+      </c>
+      <c r="D32" s="37" t="n">
+        <v>140.417</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>287.2414</v>
+      </c>
+      <c r="F32" s="39" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>0+700</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="n">
+        <v>832981.677</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>6520308.193</v>
+      </c>
+      <c r="D33" s="32" t="n">
+        <v>140.33</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>287.3026</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>0+725</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="n">
+        <v>832958.031</v>
+      </c>
+      <c r="C34" s="36" t="n">
+        <v>6520316.341</v>
+      </c>
+      <c r="D34" s="37" t="n">
+        <v>140.243</v>
+      </c>
+      <c r="E34" s="38" t="n">
+        <v>287.3616</v>
+      </c>
+      <c r="F34" s="39" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>0+750</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n">
+        <v>832934.3909999999</v>
+      </c>
+      <c r="C35" s="36" t="n">
+        <v>6520324.508</v>
+      </c>
+      <c r="D35" s="37" t="n">
+        <v>140.155</v>
+      </c>
+      <c r="E35" s="38" t="n">
+        <v>287.4182</v>
+      </c>
+      <c r="F35" s="39" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>0+775</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="n">
+        <v>832910.758</v>
+      </c>
+      <c r="C36" s="36" t="n">
+        <v>6520332.693</v>
+      </c>
+      <c r="D36" s="37" t="n">
+        <v>140.067</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>287.4725</v>
+      </c>
+      <c r="F36" s="39" t="n">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>0+800</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n">
+        <v>832887.129</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>6520340.89</v>
+      </c>
+      <c r="D37" s="32" t="n">
+        <v>139.98</v>
+      </c>
+      <c r="E37" s="33" t="n">
+        <v>287.5244</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>0+825</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n">
+        <v>832863.504</v>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>6520349.096</v>
+      </c>
+      <c r="D38" s="37" t="n">
+        <v>139.893</v>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>287.5738</v>
+      </c>
+      <c r="F38" s="39" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>0+850</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="n">
+        <v>832839.8810000001</v>
+      </c>
+      <c r="C39" s="36" t="n">
+        <v>6520357.307</v>
+      </c>
+      <c r="D39" s="37" t="n">
+        <v>139.805</v>
+      </c>
+      <c r="E39" s="38" t="n">
+        <v>287.6207</v>
+      </c>
+      <c r="F39" s="39" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>0+875</t>
+        </is>
+      </c>
+      <c r="B40" s="36" t="n">
+        <v>832816.259</v>
+      </c>
+      <c r="C40" s="36" t="n">
+        <v>6520365.521</v>
+      </c>
+      <c r="D40" s="37" t="n">
+        <v>139.718</v>
+      </c>
+      <c r="E40" s="38" t="n">
+        <v>287.6651</v>
+      </c>
+      <c r="F40" s="39" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>0+900</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>832792.637</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>6520373.732</v>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>139.63</v>
+      </c>
+      <c r="E41" s="33" t="n">
+        <v>287.7068</v>
+      </c>
+      <c r="F41" s="34" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>0+925</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="n">
+        <v>832769.014</v>
+      </c>
+      <c r="C42" s="36" t="n">
+        <v>6520381.936</v>
+      </c>
+      <c r="D42" s="37" t="n">
+        <v>139.542</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>287.7459</v>
+      </c>
+      <c r="F42" s="39" t="n">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>0+950</t>
+        </is>
+      </c>
+      <c r="B43" s="36" t="n">
+        <v>832745.387</v>
+      </c>
+      <c r="C43" s="36" t="n">
+        <v>6520390.131</v>
+      </c>
+      <c r="D43" s="37" t="n">
+        <v>139.455</v>
+      </c>
+      <c r="E43" s="38" t="n">
+        <v>287.7823</v>
+      </c>
+      <c r="F43" s="39" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>0+975</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="n">
+        <v>832721.757</v>
+      </c>
+      <c r="C44" s="36" t="n">
+        <v>6520398.312</v>
+      </c>
+      <c r="D44" s="37" t="n">
+        <v>139.368</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <v>287.816</v>
+      </c>
+      <c r="F44" s="39" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>1+000</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>832698.121</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <v>6520406.475</v>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>139.28</v>
+      </c>
+      <c r="E45" s="33" t="n">
+        <v>287.847</v>
+      </c>
+      <c r="F45" s="34" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t>IMPORTANT : Ces coordonnées sont générées automatiquement (projet démo). Remplacer par les coordonnées réelles issues du levé topographique ou du GPS.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F45"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A47:F47"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>DISTANCES TRANSVERSALES / AXE — Route Rurale 1x2 voies — 1 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>SECTION EN TRAVERS TYPE — Vue schématique (de gauche à droite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="43" t="inlineStr"/>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ← GAUCHE (distances négatives)        AXE        DROITE (distances positives) →</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ─────────────────────────────────────── 0 ────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bord_Prop_G ... Canal_G ... Bord_Chaussee_G   |   Bord_Chaussee_D ... Canal_D ... Bord_Prop_D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>Élément</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>Distance / axe (m)</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>Côté</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>Colonne cote référence</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>Onglet source</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>AXE</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>Axe</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Chaussee_G</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_G</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Chaussee_D</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_D</t>
+        </is>
+      </c>
+      <c r="E10" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>Canal_G (50x50)</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C11" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_G</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>Canal_D (50x50)</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_D</t>
+        </is>
+      </c>
+      <c r="E12" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>Accotement_G</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C13" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_G</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>Accotement_D</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_D</t>
+        </is>
+      </c>
+      <c r="E14" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_G</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="n">
+        <v>-6</v>
+      </c>
+      <c r="C15" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_G</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_D</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_D</t>
+        </is>
+      </c>
+      <c r="E16" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>UTILISATION :
+• La colonne 'Distance / axe' donne la position transversale de chaque élément (- = gauche, + = droite).
+• Combinée aux coordonnées XY de PK_Coordonnees, elle permet de calculer la position GPS de chaque élément via : X_elem = X_axe + dist × sin(gisement + 90°) / Y_elem = Y_axe + dist × cos(gisement + 90°).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1"/>
+    <row r="20" ht="18" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A18:E20"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/modeles_recepta/P4_Rural_1x2_1km.xlsx
+++ b/data/modeles_recepta/P4_Rural_1x2_1km.xlsx
@@ -1,35 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LEGENDE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PK_Coordonnees" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OFFSETS_TRANSVERSAUX" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPREVUS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROFIL_LONG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECTIONS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEGENDE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PK_Coordonnees'!$A$3:$F$45</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="+0.000;-0.000;0.000"/>
-  </numFmts>
-  <fonts count="21">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +45,24 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="009CA3AF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="7"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0000FFFF"/>
       <sz val="12"/>
@@ -72,77 +83,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0064748B"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001E293B"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <b val="1"/>
-      <color rgb="000F4C35"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="00475569"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F766E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000F766E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -211,27 +153,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1F38"/>
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
+        <fgColor rgb="00374151"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="004B5563"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F9FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -241,31 +188,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F4C35"/>
+        <fgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0FDF4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0FFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="000D1F38"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -289,23 +221,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -343,125 +303,87 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,6 +459,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4546,6 +4498,988 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_BB</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_GNT</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_Fond_Forme</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>G_BB_Roulement</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>G_GNT_Base</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>G_Fond_Forme</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>G_Bordure_Finie</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>G_Tablier_Fini_50x50</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>G_Radier_Interieur</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>G_Beton_Proprete</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>G_Fond_Fouille</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>G_Bord_Propriete</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>D_BB_Roulement</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>D_GNT_Base</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>D_Fond_Forme</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>D_Bordure_Finie</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>D_Tablier_Fini_50x50</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>D_Radier_Interieur</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>D_Beton_Proprete</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>D_Fond_Fouille</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>D_Bord_Propriete</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>0+012</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="J2" s="15" t="n">
+        <v>85.27</v>
+      </c>
+      <c r="K2" s="15" t="n">
+        <v>85.17</v>
+      </c>
+      <c r="L2" s="15" t="n">
+        <v>84.97</v>
+      </c>
+      <c r="M2" s="15" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="N2" s="15" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="O2" s="15" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="P2" s="15" t="n">
+        <v>85.58</v>
+      </c>
+      <c r="Q2" s="15" t="n">
+        <v>85.81</v>
+      </c>
+      <c r="R2" s="15" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="S2" s="15" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="T2" s="15" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="U2" s="15" t="n">
+        <v>84.93000000000001</v>
+      </c>
+      <c r="V2" s="15" t="n">
+        <v>86.03</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>0+040</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>86.41</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>85.73</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>85.53</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="P3" s="15" t="n">
+        <v>86.14</v>
+      </c>
+      <c r="Q3" s="15" t="n">
+        <v>86.37</v>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>86.59</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>0+068</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>87.06</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>86.29000000000001</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="M4" s="15" t="n">
+        <v>87.19</v>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="P4" s="15" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="Q4" s="15" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="R4" s="15" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="S4" s="15" t="n">
+        <v>86.34999999999999</v>
+      </c>
+      <c r="T4" s="15" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="U4" s="15" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="V4" s="15" t="n">
+        <v>87.15000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Z_axe (m NGF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>0+000</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n">
+        <v>85.75</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>0+025</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>86.25</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>0+050</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>86.75</v>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>0+075</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>87.25</v>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>0+100</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>87.75</v>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>0+125</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>88.25</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>0+150</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>88.75</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>0+175</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>89.25</v>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>0+200</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>89.75</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>0+225</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>90.25</v>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>0+250</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>90.75</v>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>0+275</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>91.25</v>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>0+300</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>91.75</v>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>0+325</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>92.25</v>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>0+350</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>92.75</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>0+375</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>93.25</v>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>0+400</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>0+425</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>94.25</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>0+450</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>94.75</v>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>0+475</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>95.25</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>0+500</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>95.75</v>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>0+525</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>96.25</v>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>0+550</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>0+575</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>97.25</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>0+600</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>97.75</v>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>0+625</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>98.25</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>0+650</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>98.75</v>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>0+675</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>99.25</v>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>0+700</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>99.75</v>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>0+725</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>100.25</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>0+750</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>100.75</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>0+775</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>101.25</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>0+800</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>101.75</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>0+825</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>102.25</v>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>0+850</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>102.75</v>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>0+875</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="n">
+        <v>103.25</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>0+900</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>103.75</v>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>0+925</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>104.25</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>0+950</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>104.75</v>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>0+975</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>105.25</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>1+000</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>105.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>SECTIONS — Paramètres variables par tronçon  |  Ajouter une ligne si épaisseurs / dévers / distances changent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Nom_Section</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>PK_debut</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>PK_fin</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>e_BB_m</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>e_GB4_m</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>e_GNT_m</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>e_FF_m</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>Devers_G_pct</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>Devers_D_pct</t>
+        </is>
+      </c>
+      <c r="K2" s="22" t="inlineStr">
+        <is>
+          <t>Dist_G_m</t>
+        </is>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>Dist_D_m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Section principale</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>0+000</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>1+000</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="24" t="n"/>
+      <c r="G3" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="26" t="inlineStr"/>
+      <c r="C4" s="26" t="inlineStr"/>
+      <c r="D4" s="26" t="inlineStr"/>
+      <c r="E4" s="26" t="inlineStr"/>
+      <c r="F4" s="26" t="inlineStr"/>
+      <c r="G4" s="26" t="inlineStr"/>
+      <c r="H4" s="26" t="inlineStr"/>
+      <c r="I4" s="26" t="inlineStr"/>
+      <c r="J4" s="26" t="inlineStr"/>
+      <c r="K4" s="26" t="inlineStr"/>
+      <c r="L4" s="26" t="inlineStr"/>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="26" t="inlineStr"/>
+      <c r="C5" s="26" t="inlineStr"/>
+      <c r="D5" s="26" t="inlineStr"/>
+      <c r="E5" s="26" t="inlineStr"/>
+      <c r="F5" s="26" t="inlineStr"/>
+      <c r="G5" s="26" t="inlineStr"/>
+      <c r="H5" s="26" t="inlineStr"/>
+      <c r="I5" s="26" t="inlineStr"/>
+      <c r="J5" s="26" t="inlineStr"/>
+      <c r="K5" s="26" t="inlineStr"/>
+      <c r="L5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Légende : e_BB/GB4/GNT/FF en mètres  |  Devers_G/D en %  |  Dist_G/D = distance axe→bord en m  |  e_GB4 vide = couche absente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B25:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4577,338 +5511,338 @@
     <row r="23" ht="17" customHeight="1"/>
     <row r="24" ht="17" customHeight="1"/>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>SPECIFICATIONS DU PROJET</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Titre:          Route Rurale Secondaire 1x2 voies</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Devers:         G:3.0% | D:4.0%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Largeurs:       2x3.0m voies + 1.0m accotement | dist axe/bord = 4.0m</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Couches:        BB 5cm / GNT 20cm / Fond de Forme 25cm</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pente long.:    2.0%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cote axe Z0:    85.750 m NGF</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  PK debut/fin:   0+000 / 1+000</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pas PK:         25 m</t>
         </is>
       </c>
     </row>
     <row r="35" ht="11" customHeight="1">
-      <c r="B35" s="15" t="inlineStr"/>
+      <c r="B35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>ASSAINISSEMENT GAUCHE — 50x50 (H=0.50m)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Caniveau macon 50x50 — H int=0.50m / dalle=10cm / radier=10cm / BP=20cm</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>ASSAINISSEMENT DROIT  — 50x50 (H=0.50m)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Caniveau macon 50x50 — H int=0.50m / dalle=10cm / radier=10cm / BP=20cm</t>
         </is>
       </c>
     </row>
     <row r="40" ht="11" customHeight="1">
-      <c r="B40" s="15" t="inlineStr"/>
+      <c r="B40" s="30" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>STRATIGRAPHIE ASSAINISSEMENT (de bas en haut) :</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  Fond de Fouille                         (cote la plus basse)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + 20 cm  → Beton de Proprete (BP)       dessus de la couche de 20cm</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + 10 cm  → Radier Interieur             interieur fond du caniveau</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + H canal (100 / 80 / 60 / 50 cm...)   hauteur utile interieure</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + e dalle                               Tablier Fini = bord chaussee</t>
         </is>
       </c>
     </row>
     <row r="47" ht="11" customHeight="1">
-      <c r="B47" s="15" t="inlineStr"/>
+      <c r="B47" s="30" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="37" t="inlineStr">
         <is>
           <t>COLONNES COTE_GAUCHE</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  PK</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_BB</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_GNT</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_BB_Roulement</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_GNT_Base</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B55" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Bordure_Finie</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Tablier_Fini_50x50</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Radier_Interieur</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Beton_Proprete</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Fond_Fouille</t>
         </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Bord_Propriete</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>COLONNES COTE_DROIT</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
-      <c r="B63" s="25" t="inlineStr">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  PK</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
-      <c r="B64" s="25" t="inlineStr">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_BB</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="B65" s="25" t="inlineStr">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_GNT</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="B66" s="25" t="inlineStr">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
-      <c r="B67" s="25" t="inlineStr">
+      <c r="B67" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_BB_Roulement</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
-      <c r="B68" s="25" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_GNT_Base</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
-      <c r="B69" s="25" t="inlineStr">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
-      <c r="B70" s="25" t="inlineStr">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Bordure_Finie</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
-      <c r="B71" s="25" t="inlineStr">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Tablier_Fini_50x50</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
-      <c r="B72" s="25" t="inlineStr">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Radier_Interieur</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
-      <c r="B73" s="25" t="inlineStr">
+      <c r="B73" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Beton_Proprete</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
-      <c r="B74" s="25" t="inlineStr">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Fond_Fouille</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
-      <c r="B75" s="25" t="inlineStr">
+      <c r="B75" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Bord_Propriete</t>
         </is>
@@ -4916,1351 +5850,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>COORDONNÉES DE L'AXE — Route Rurale 1x2 voies — 1 km</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>Système de référence : Lambert 93 (EPSG:2154)  —  Données à renseigner avec les coordonnées réelles du levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
-        <is>
-          <t>X (m)</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>Y (m)</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>Z axe (m)</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
-        <is>
-          <t>Gisement (°)</t>
-        </is>
-      </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>Dist. cumulée (m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>Point kilométrique</t>
-        </is>
-      </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Lambert 93 — Est</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>Lambert 93 — Nord</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
-        <is>
-          <t>Cote NGF de l'axe chaussée</t>
-        </is>
-      </c>
-      <c r="E4" s="29" t="inlineStr">
-        <is>
-          <t>Direction route (0°=N, 90°=E)</t>
-        </is>
-      </c>
-      <c r="F4" s="29" t="inlineStr">
-        <is>
-          <t>Distance depuis l'origine</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>0+000</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="n">
-        <v>833650</v>
-      </c>
-      <c r="C5" s="31" t="n">
-        <v>6520100</v>
-      </c>
-      <c r="D5" s="32" t="n">
-        <v>142.78</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>285</v>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>0+025</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="n">
-        <v>833625.862</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>6520106.51</v>
-      </c>
-      <c r="D6" s="37" t="n">
-        <v>142.692</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>285.0937</v>
-      </c>
-      <c r="F6" s="39" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>0+050</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="n">
-        <v>833601.746</v>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>6520113.099</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>142.605</v>
-      </c>
-      <c r="E7" s="38" t="n">
-        <v>285.1874</v>
-      </c>
-      <c r="F7" s="39" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>0+075</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="n">
-        <v>833577.652</v>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>6520119.766</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>142.518</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>285.2808</v>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>0+100</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="n">
-        <v>833553.578</v>
-      </c>
-      <c r="C9" s="31" t="n">
-        <v>6520126.512</v>
-      </c>
-      <c r="D9" s="32" t="n">
-        <v>142.43</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>285.374</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>0+125</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>833529.527</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>6520133.335</v>
-      </c>
-      <c r="D10" s="37" t="n">
-        <v>142.343</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>285.4668</v>
-      </c>
-      <c r="F10" s="39" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>0+150</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>833505.497</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>6520140.235</v>
-      </c>
-      <c r="D11" s="37" t="n">
-        <v>142.255</v>
-      </c>
-      <c r="E11" s="38" t="n">
-        <v>285.5592</v>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>0+175</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>833481.4889999999</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>6520147.211</v>
-      </c>
-      <c r="D12" s="37" t="n">
-        <v>142.167</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>285.651</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>0+200</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="n">
-        <v>833457.502</v>
-      </c>
-      <c r="C13" s="31" t="n">
-        <v>6520154.262</v>
-      </c>
-      <c r="D13" s="32" t="n">
-        <v>142.08</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>285.7422</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>0+225</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="n">
-        <v>833433.536</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>6520161.386</v>
-      </c>
-      <c r="D14" s="37" t="n">
-        <v>141.993</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>285.8327</v>
-      </c>
-      <c r="F14" s="39" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>0+250</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="n">
-        <v>833409.591</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>6520168.583</v>
-      </c>
-      <c r="D15" s="37" t="n">
-        <v>141.905</v>
-      </c>
-      <c r="E15" s="38" t="n">
-        <v>285.9223</v>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>0+275</t>
-        </is>
-      </c>
-      <c r="B16" s="36" t="n">
-        <v>833385.6679999999</v>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>6520175.851</v>
-      </c>
-      <c r="D16" s="37" t="n">
-        <v>141.817</v>
-      </c>
-      <c r="E16" s="38" t="n">
-        <v>286.0111</v>
-      </c>
-      <c r="F16" s="39" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>0+300</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="n">
-        <v>833361.765</v>
-      </c>
-      <c r="C17" s="31" t="n">
-        <v>6520183.188</v>
-      </c>
-      <c r="D17" s="32" t="n">
-        <v>141.73</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>286.0988</v>
-      </c>
-      <c r="F17" s="34" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>0+325</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="n">
-        <v>833337.882</v>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>6520190.593</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <v>141.643</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>286.1855</v>
-      </c>
-      <c r="F18" s="39" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>0+350</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="n">
-        <v>833314.019</v>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>6520198.063</v>
-      </c>
-      <c r="D19" s="37" t="n">
-        <v>141.555</v>
-      </c>
-      <c r="E19" s="38" t="n">
-        <v>286.271</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>0+375</t>
-        </is>
-      </c>
-      <c r="B20" s="36" t="n">
-        <v>833290.175</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>6520205.597</v>
-      </c>
-      <c r="D20" s="37" t="n">
-        <v>141.468</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>286.3553</v>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>0+400</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="n">
-        <v>833266.35</v>
-      </c>
-      <c r="C21" s="31" t="n">
-        <v>6520213.193</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>141.38</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>286.4383</v>
-      </c>
-      <c r="F21" s="34" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>0+425</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="n">
-        <v>833242.5429999999</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>6520220.848</v>
-      </c>
-      <c r="D22" s="37" t="n">
-        <v>141.292</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>286.5198</v>
-      </c>
-      <c r="F22" s="39" t="n">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>0+450</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="n">
-        <v>833218.755</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>6520228.559</v>
-      </c>
-      <c r="D23" s="37" t="n">
-        <v>141.205</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <v>286.5999</v>
-      </c>
-      <c r="F23" s="39" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>0+475</t>
-        </is>
-      </c>
-      <c r="B24" s="36" t="n">
-        <v>833194.983</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>6520236.325</v>
-      </c>
-      <c r="D24" s="37" t="n">
-        <v>141.118</v>
-      </c>
-      <c r="E24" s="38" t="n">
-        <v>286.6784</v>
-      </c>
-      <c r="F24" s="39" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>0+500</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="n">
-        <v>833171.228</v>
-      </c>
-      <c r="C25" s="31" t="n">
-        <v>6520244.142</v>
-      </c>
-      <c r="D25" s="32" t="n">
-        <v>141.03</v>
-      </c>
-      <c r="E25" s="33" t="n">
-        <v>286.7553</v>
-      </c>
-      <c r="F25" s="34" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>0+525</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>833147.488</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>6520252.009</v>
-      </c>
-      <c r="D26" s="37" t="n">
-        <v>140.942</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <v>286.8305</v>
-      </c>
-      <c r="F26" s="39" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="inlineStr">
-        <is>
-          <t>0+550</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="n">
-        <v>833123.763</v>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>6520259.921</v>
-      </c>
-      <c r="D27" s="37" t="n">
-        <v>140.855</v>
-      </c>
-      <c r="E27" s="38" t="n">
-        <v>286.9038</v>
-      </c>
-      <c r="F27" s="39" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="35" t="inlineStr">
-        <is>
-          <t>0+575</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>833100.052</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>6520267.877</v>
-      </c>
-      <c r="D28" s="37" t="n">
-        <v>140.768</v>
-      </c>
-      <c r="E28" s="38" t="n">
-        <v>286.9753</v>
-      </c>
-      <c r="F28" s="39" t="n">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>0+600</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="n">
-        <v>833076.355</v>
-      </c>
-      <c r="C29" s="31" t="n">
-        <v>6520275.873</v>
-      </c>
-      <c r="D29" s="32" t="n">
-        <v>140.68</v>
-      </c>
-      <c r="E29" s="33" t="n">
-        <v>287.0449</v>
-      </c>
-      <c r="F29" s="34" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t>0+625</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n">
-        <v>833052.669</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>6520283.906</v>
-      </c>
-      <c r="D30" s="37" t="n">
-        <v>140.593</v>
-      </c>
-      <c r="E30" s="38" t="n">
-        <v>287.1125</v>
-      </c>
-      <c r="F30" s="39" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="35" t="inlineStr">
-        <is>
-          <t>0+650</t>
-        </is>
-      </c>
-      <c r="B31" s="36" t="n">
-        <v>833028.995</v>
-      </c>
-      <c r="C31" s="36" t="n">
-        <v>6520291.972</v>
-      </c>
-      <c r="D31" s="37" t="n">
-        <v>140.505</v>
-      </c>
-      <c r="E31" s="38" t="n">
-        <v>287.178</v>
-      </c>
-      <c r="F31" s="39" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>0+675</t>
-        </is>
-      </c>
-      <c r="B32" s="36" t="n">
-        <v>833005.3320000001</v>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>6520300.069</v>
-      </c>
-      <c r="D32" s="37" t="n">
-        <v>140.417</v>
-      </c>
-      <c r="E32" s="38" t="n">
-        <v>287.2414</v>
-      </c>
-      <c r="F32" s="39" t="n">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>0+700</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
-        <v>832981.677</v>
-      </c>
-      <c r="C33" s="31" t="n">
-        <v>6520308.193</v>
-      </c>
-      <c r="D33" s="32" t="n">
-        <v>140.33</v>
-      </c>
-      <c r="E33" s="33" t="n">
-        <v>287.3026</v>
-      </c>
-      <c r="F33" s="34" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>0+725</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="n">
-        <v>832958.031</v>
-      </c>
-      <c r="C34" s="36" t="n">
-        <v>6520316.341</v>
-      </c>
-      <c r="D34" s="37" t="n">
-        <v>140.243</v>
-      </c>
-      <c r="E34" s="38" t="n">
-        <v>287.3616</v>
-      </c>
-      <c r="F34" s="39" t="n">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>0+750</t>
-        </is>
-      </c>
-      <c r="B35" s="36" t="n">
-        <v>832934.3909999999</v>
-      </c>
-      <c r="C35" s="36" t="n">
-        <v>6520324.508</v>
-      </c>
-      <c r="D35" s="37" t="n">
-        <v>140.155</v>
-      </c>
-      <c r="E35" s="38" t="n">
-        <v>287.4182</v>
-      </c>
-      <c r="F35" s="39" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="35" t="inlineStr">
-        <is>
-          <t>0+775</t>
-        </is>
-      </c>
-      <c r="B36" s="36" t="n">
-        <v>832910.758</v>
-      </c>
-      <c r="C36" s="36" t="n">
-        <v>6520332.693</v>
-      </c>
-      <c r="D36" s="37" t="n">
-        <v>140.067</v>
-      </c>
-      <c r="E36" s="38" t="n">
-        <v>287.4725</v>
-      </c>
-      <c r="F36" s="39" t="n">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>0+800</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="n">
-        <v>832887.129</v>
-      </c>
-      <c r="C37" s="31" t="n">
-        <v>6520340.89</v>
-      </c>
-      <c r="D37" s="32" t="n">
-        <v>139.98</v>
-      </c>
-      <c r="E37" s="33" t="n">
-        <v>287.5244</v>
-      </c>
-      <c r="F37" s="34" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="inlineStr">
-        <is>
-          <t>0+825</t>
-        </is>
-      </c>
-      <c r="B38" s="36" t="n">
-        <v>832863.504</v>
-      </c>
-      <c r="C38" s="36" t="n">
-        <v>6520349.096</v>
-      </c>
-      <c r="D38" s="37" t="n">
-        <v>139.893</v>
-      </c>
-      <c r="E38" s="38" t="n">
-        <v>287.5738</v>
-      </c>
-      <c r="F38" s="39" t="n">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="inlineStr">
-        <is>
-          <t>0+850</t>
-        </is>
-      </c>
-      <c r="B39" s="36" t="n">
-        <v>832839.8810000001</v>
-      </c>
-      <c r="C39" s="36" t="n">
-        <v>6520357.307</v>
-      </c>
-      <c r="D39" s="37" t="n">
-        <v>139.805</v>
-      </c>
-      <c r="E39" s="38" t="n">
-        <v>287.6207</v>
-      </c>
-      <c r="F39" s="39" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
-        <is>
-          <t>0+875</t>
-        </is>
-      </c>
-      <c r="B40" s="36" t="n">
-        <v>832816.259</v>
-      </c>
-      <c r="C40" s="36" t="n">
-        <v>6520365.521</v>
-      </c>
-      <c r="D40" s="37" t="n">
-        <v>139.718</v>
-      </c>
-      <c r="E40" s="38" t="n">
-        <v>287.6651</v>
-      </c>
-      <c r="F40" s="39" t="n">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>0+900</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>832792.637</v>
-      </c>
-      <c r="C41" s="31" t="n">
-        <v>6520373.732</v>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>139.63</v>
-      </c>
-      <c r="E41" s="33" t="n">
-        <v>287.7068</v>
-      </c>
-      <c r="F41" s="34" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="inlineStr">
-        <is>
-          <t>0+925</t>
-        </is>
-      </c>
-      <c r="B42" s="36" t="n">
-        <v>832769.014</v>
-      </c>
-      <c r="C42" s="36" t="n">
-        <v>6520381.936</v>
-      </c>
-      <c r="D42" s="37" t="n">
-        <v>139.542</v>
-      </c>
-      <c r="E42" s="38" t="n">
-        <v>287.7459</v>
-      </c>
-      <c r="F42" s="39" t="n">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="35" t="inlineStr">
-        <is>
-          <t>0+950</t>
-        </is>
-      </c>
-      <c r="B43" s="36" t="n">
-        <v>832745.387</v>
-      </c>
-      <c r="C43" s="36" t="n">
-        <v>6520390.131</v>
-      </c>
-      <c r="D43" s="37" t="n">
-        <v>139.455</v>
-      </c>
-      <c r="E43" s="38" t="n">
-        <v>287.7823</v>
-      </c>
-      <c r="F43" s="39" t="n">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="35" t="inlineStr">
-        <is>
-          <t>0+975</t>
-        </is>
-      </c>
-      <c r="B44" s="36" t="n">
-        <v>832721.757</v>
-      </c>
-      <c r="C44" s="36" t="n">
-        <v>6520398.312</v>
-      </c>
-      <c r="D44" s="37" t="n">
-        <v>139.368</v>
-      </c>
-      <c r="E44" s="38" t="n">
-        <v>287.816</v>
-      </c>
-      <c r="F44" s="39" t="n">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t>1+000</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="n">
-        <v>832698.121</v>
-      </c>
-      <c r="C45" s="31" t="n">
-        <v>6520406.475</v>
-      </c>
-      <c r="D45" s="32" t="n">
-        <v>139.28</v>
-      </c>
-      <c r="E45" s="33" t="n">
-        <v>287.847</v>
-      </c>
-      <c r="F45" s="34" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="40" t="inlineStr">
-        <is>
-          <t>IMPORTANT : Ces coordonnées sont générées automatiquement (projet démo). Remplacer par les coordonnées réelles issues du levé topographique ou du GPS.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:F45"/>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A47:F47"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>DISTANCES TRANSVERSALES / AXE — Route Rurale 1x2 voies — 1 km</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
-        <is>
-          <t>SECTION EN TRAVERS TYPE — Vue schématique (de gauche à droite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="43" t="inlineStr"/>
-    </row>
-    <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ← GAUCHE (distances négatives)        AXE        DROITE (distances positives) →</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ─────────────────────────────────────── 0 ────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Bord_Prop_G ... Canal_G ... Bord_Chaussee_G   |   Bord_Chaussee_D ... Canal_D ... Bord_Prop_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>Élément</t>
-        </is>
-      </c>
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>Distance / axe (m)</t>
-        </is>
-      </c>
-      <c r="C7" s="44" t="inlineStr">
-        <is>
-          <t>Côté</t>
-        </is>
-      </c>
-      <c r="D7" s="44" t="inlineStr">
-        <is>
-          <t>Colonne cote référence</t>
-        </is>
-      </c>
-      <c r="E7" s="44" t="inlineStr">
-        <is>
-          <t>Onglet source</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t>AXE</t>
-        </is>
-      </c>
-      <c r="B8" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
-        <is>
-          <t>Axe</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Chaussee_G</t>
-        </is>
-      </c>
-      <c r="B9" s="49" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_G</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Chaussee_D</t>
-        </is>
-      </c>
-      <c r="B10" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D10" s="50" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_D</t>
-        </is>
-      </c>
-      <c r="E10" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="48" t="inlineStr">
-        <is>
-          <t>Canal_G (50x50)</t>
-        </is>
-      </c>
-      <c r="B11" s="49" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C11" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_G</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t>Canal_D (50x50)</t>
-        </is>
-      </c>
-      <c r="B12" s="51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C12" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D12" s="50" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_D</t>
-        </is>
-      </c>
-      <c r="E12" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="48" t="inlineStr">
-        <is>
-          <t>Accotement_G</t>
-        </is>
-      </c>
-      <c r="B13" s="49" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="C13" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_G</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="50" t="inlineStr">
-        <is>
-          <t>Accotement_D</t>
-        </is>
-      </c>
-      <c r="B14" s="51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C14" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D14" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_D</t>
-        </is>
-      </c>
-      <c r="E14" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_G</t>
-        </is>
-      </c>
-      <c r="B15" s="49" t="n">
-        <v>-6</v>
-      </c>
-      <c r="C15" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_G</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_D</t>
-        </is>
-      </c>
-      <c r="B16" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D16" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_D</t>
-        </is>
-      </c>
-      <c r="E16" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="52" t="inlineStr">
-        <is>
-          <t>UTILISATION :
-• La colonne 'Distance / axe' donne la position transversale de chaque élément (- = gauche, + = droite).
-• Combinée aux coordonnées XY de PK_Coordonnees, elle permet de calculer la position GPS de chaque élément via : X_elem = X_axe + dist × sin(gisement + 90°) / Y_elem = Y_axe + dist × cos(gisement + 90°).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1"/>
-    <row r="20" ht="18" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A18:E20"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:E3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>